--- a/projects/project-3/assignment/src/data/qudt-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/qudt-axioms.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb1</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b1</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb3</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b3</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb4</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b4</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb5</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b5</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb6</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b6</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb7</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b7</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb8</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b8</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb10</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b10</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb11</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b11</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb12</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b12</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb13</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b13</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb14</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b14</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb15</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b15</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb16</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b16</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb17</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b17</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb18</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b18</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb19</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b19</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb20</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b20</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb21</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b21</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb22</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b22</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb23</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b23</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb24</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b24</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb25</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b25</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb26</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b26</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb27</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b27</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb29</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b29</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb30</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b30</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb31</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b31</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb32</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b32</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb33</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b33</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb34</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b34</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb35</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b35</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb36</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b36</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb37</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b37</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb38</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b38</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb39</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b39</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb40</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b40</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb41</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b41</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n017afa139f8541c0b787114b0e9af9acb42</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf na6695444ba404f44a022ff7f346c9465b42</t>
         </is>
       </c>
     </row>
